--- a/data/trans_orig/P1404-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1404-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de colesterol alto en 2007</t>
+          <t>Población con diagnóstico de colesterol alto en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33416</t>
+          <t>34675</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60045</t>
+          <t>61043</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>55299</t>
+          <t>54375</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>85562</t>
+          <t>85988</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>98335</t>
+          <t>96930</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>138375</t>
+          <t>136712</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>633967</t>
+          <t>632969</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>660596</t>
+          <t>659337</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>602789</t>
+          <t>602363</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>633052</t>
+          <t>633976</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1243988</t>
+          <t>1245651</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1284028</t>
+          <t>1285433</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,99%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71254</t>
+          <t>69661</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>106268</t>
+          <t>106463</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>91042</t>
+          <t>91756</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>131654</t>
+          <t>132071</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>170665</t>
+          <t>170199</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>225173</t>
+          <t>224647</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>855532</t>
+          <t>855337</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>890546</t>
+          <t>892139</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>836739</t>
+          <t>836322</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>877351</t>
+          <t>876637</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1705020</t>
+          <t>1705546</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1759528</t>
+          <t>1759994</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,18%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37663</t>
+          <t>37555</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64521</t>
+          <t>64885</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60094</t>
+          <t>59165</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>90999</t>
+          <t>91013</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>105667</t>
+          <t>105260</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>146308</t>
+          <t>146761</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>613988</t>
+          <t>613624</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>640846</t>
+          <t>640954</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>592842</t>
+          <t>592828</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>623747</t>
+          <t>624676</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1216042</t>
+          <t>1215589</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1256683</t>
+          <t>1257090</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,27%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63321</t>
+          <t>61799</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93858</t>
+          <t>93731</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>76901</t>
+          <t>78061</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>113586</t>
+          <t>114368</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>147380</t>
+          <t>149355</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>198565</t>
+          <t>197823</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>848364</t>
+          <t>848491</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>878901</t>
+          <t>880423</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>925026</t>
+          <t>924244</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>961711</t>
+          <t>960551</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1782269</t>
+          <t>1783011</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1833454</t>
+          <t>1831479</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,46%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>231228</t>
+          <t>229997</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>294029</t>
+          <t>291763</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>314712</t>
+          <t>312640</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>383461</t>
+          <t>385338</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>561745</t>
+          <t>561635</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>655564</t>
+          <t>658087</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2982514</t>
+          <t>2984780</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3045315</t>
+          <t>3046546</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2995736</t>
+          <t>2993859</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3064485</t>
+          <t>3066557</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6000177</t>
+          <t>5997654</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6093996</t>
+          <t>6094106</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de colesterol alto en 2012</t>
+          <t>Población con diagnóstico de colesterol alto en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74267</t>
+          <t>75195</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>110788</t>
+          <t>110301</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>86401</t>
+          <t>86637</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>126163</t>
+          <t>127587</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>170155</t>
+          <t>173186</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>223091</t>
+          <t>226040</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>592681</t>
+          <t>593168</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>629202</t>
+          <t>628274</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>570887</t>
+          <t>569463</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>610649</t>
+          <t>610413</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1177428</t>
+          <t>1174479</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1230364</t>
+          <t>1227333</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,63%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>98240</t>
+          <t>95793</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>138281</t>
+          <t>136128</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>123135</t>
+          <t>122974</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>168045</t>
+          <t>168813</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>229828</t>
+          <t>231983</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>293388</t>
+          <t>292758</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>879666</t>
+          <t>881819</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>919707</t>
+          <t>922154</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>860928</t>
+          <t>860160</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>905838</t>
+          <t>905999</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1753533</t>
+          <t>1754163</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1817093</t>
+          <t>1814938</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,67%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59310</t>
+          <t>59330</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>96154</t>
+          <t>96565</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79644</t>
+          <t>81082</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>119802</t>
+          <t>120011</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>150996</t>
+          <t>150866</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>202651</t>
+          <t>208958</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>660061</t>
+          <t>659650</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>696905</t>
+          <t>696885</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>657372</t>
+          <t>657163</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>697530</t>
+          <t>696092</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1330738</t>
+          <t>1324431</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1382393</t>
+          <t>1382523</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,16%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87444</t>
+          <t>84995</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>126405</t>
+          <t>127349</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>118707</t>
+          <t>119954</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>165581</t>
+          <t>167834</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>219597</t>
+          <t>215348</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>284329</t>
+          <t>276389</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>821334</t>
+          <t>820390</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>860295</t>
+          <t>862744</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>886320</t>
+          <t>884067</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>933194</t>
+          <t>931947</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1715311</t>
+          <t>1723251</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1780043</t>
+          <t>1784292</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,23%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>350005</t>
+          <t>349516</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>433817</t>
+          <t>429276</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>451920</t>
+          <t>448403</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>534745</t>
+          <t>533428</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>825046</t>
+          <t>822841</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>935506</t>
+          <t>934543</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2991553</t>
+          <t>2996094</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3075365</t>
+          <t>3075854</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3020353</t>
+          <t>3021670</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3103178</t>
+          <t>3106695</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6044963</t>
+          <t>6045926</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6155423</t>
+          <t>6157628</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,21%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de colesterol alto en 2016</t>
+          <t>Población con diagnóstico de colesterol alto en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>69344</t>
+          <t>69148</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>102270</t>
+          <t>105302</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>83753</t>
+          <t>83832</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>121582</t>
+          <t>122660</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>161865</t>
+          <t>160806</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>210376</t>
+          <t>211512</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,7%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>572530</t>
+          <t>569498</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>605456</t>
+          <t>605652</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>551257</t>
+          <t>550179</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>589086</t>
+          <t>589007</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1137263</t>
+          <t>1136127</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1185774</t>
+          <t>1186833</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>88,07%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>103992</t>
+          <t>101351</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>146601</t>
+          <t>143163</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>131521</t>
+          <t>129565</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>178776</t>
+          <t>177231</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>244136</t>
+          <t>244271</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>309862</t>
+          <t>310549</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>875830</t>
+          <t>879268</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>918439</t>
+          <t>921080</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>864137</t>
+          <t>865682</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>911392</t>
+          <t>913348</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1755482</t>
+          <t>1754795</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1821208</t>
+          <t>1821073</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,17%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77748</t>
+          <t>76988</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>114226</t>
+          <t>114616</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>70260</t>
+          <t>69071</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>105460</t>
+          <t>106560</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>155780</t>
+          <t>159119</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>208771</t>
+          <t>209647</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>645326</t>
+          <t>644936</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>681804</t>
+          <t>682564</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>679551</t>
+          <t>678451</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>714751</t>
+          <t>715940</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1335792</t>
+          <t>1334916</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1388783</t>
+          <t>1385444</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,7%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70298</t>
+          <t>71013</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>105732</t>
+          <t>106571</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>105398</t>
+          <t>105439</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>147767</t>
+          <t>151817</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>185239</t>
+          <t>185117</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>243163</t>
+          <t>244724</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>831835</t>
+          <t>830996</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>867269</t>
+          <t>866554</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>896012</t>
+          <t>891962</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>938381</t>
+          <t>938340</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1738183</t>
+          <t>1736622</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1796107</t>
+          <t>1796229</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,66%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>353120</t>
+          <t>353501</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>427140</t>
+          <t>427026</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>428174</t>
+          <t>428803</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>512181</t>
+          <t>514035</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>803469</t>
+          <t>802335</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>919823</t>
+          <t>915480</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2967210</t>
+          <t>2967324</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3041230</t>
+          <t>3040849</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3032361</t>
+          <t>3030507</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3116368</t>
+          <t>3115739</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6019069</t>
+          <t>6023412</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6135423</t>
+          <t>6136557</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,44%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de colesterol alto en 2023</t>
+          <t>Población con diagnóstico de colesterol alto en 2023 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>77612</t>
+          <t>79557</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>112089</t>
+          <t>113500</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>105546</t>
+          <t>106029</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>132844</t>
+          <t>133175</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>192363</t>
+          <t>191591</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>235283</t>
+          <t>235167</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,7 +6659,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>522803</t>
+          <t>521392</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>557280</t>
+          <t>555335</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>541993</t>
+          <t>541662</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>569291</t>
+          <t>568808</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1074446</t>
+          <t>1074562</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1117366</t>
+          <t>1118138</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,37%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>75807</t>
+          <t>58849</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>174153</t>
+          <t>175020</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>134261</t>
+          <t>132979</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>168734</t>
+          <t>167354</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>186772</t>
+          <t>188914</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>326748</t>
+          <t>325095</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1016582</t>
+          <t>1015715</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1114928</t>
+          <t>1131886</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>786548</t>
+          <t>787928</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>821021</t>
+          <t>822303</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1819269</t>
+          <t>1820922</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1959245</t>
+          <t>1957103</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,2%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89019</t>
+          <t>90095</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>129162</t>
+          <t>128481</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>113557</t>
+          <t>115399</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>580340</t>
+          <t>610314</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>220859</t>
+          <t>222962</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>832209</t>
+          <t>856711</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>52,5%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>570892</t>
+          <t>571573</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>611035</t>
+          <t>609959</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>351499</t>
+          <t>321525</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>818282</t>
+          <t>816440</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>799684</t>
+          <t>775182</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1411034</t>
+          <t>1408931</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,34%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>111713</t>
+          <t>111372</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>150961</t>
+          <t>148859</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>149098</t>
+          <t>152801</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>211678</t>
+          <t>213090</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>279825</t>
+          <t>280104</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>347547</t>
+          <t>348317</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,27%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>775137</t>
+          <t>777239</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>814385</t>
+          <t>814726</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>879219</t>
+          <t>877807</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>941799</t>
+          <t>938096</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1669448</t>
+          <t>1668678</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1737170</t>
+          <t>1736891</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,11%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>363541</t>
+          <t>365988</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>518525</t>
+          <t>515380</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>570321</t>
+          <t>572572</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1395833</t>
+          <t>1282956</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1017635</t>
+          <t>1019748</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1838309</t>
+          <t>1924356</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>27,09%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2933255</t>
+          <t>2936400</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3088239</t>
+          <t>3085792</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2257022</t>
+          <t>2369899</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3082534</t>
+          <t>3080283</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5266326</t>
+          <t>5180279</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6087000</t>
+          <t>6084887</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1404-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1404-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34675</t>
+          <t>34478</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61043</t>
+          <t>61587</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54375</t>
+          <t>53918</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>85988</t>
+          <t>84767</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>96930</t>
+          <t>95639</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>136712</t>
+          <t>134785</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>632969</t>
+          <t>632425</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>659337</t>
+          <t>659534</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>602363</t>
+          <t>603584</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>633976</t>
+          <t>634433</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1245651</t>
+          <t>1247578</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1285433</t>
+          <t>1286724</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,08%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69661</t>
+          <t>70870</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>106463</t>
+          <t>106357</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>91756</t>
+          <t>92420</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>132071</t>
+          <t>132209</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>170199</t>
+          <t>171318</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>224647</t>
+          <t>225877</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>855337</t>
+          <t>855443</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>892139</t>
+          <t>890930</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>836322</t>
+          <t>836184</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>876637</t>
+          <t>875973</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1705546</t>
+          <t>1704316</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1759994</t>
+          <t>1758875</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,12%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37555</t>
+          <t>38036</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64885</t>
+          <t>64565</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59165</t>
+          <t>59557</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>91013</t>
+          <t>91591</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>105260</t>
+          <t>106104</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>146761</t>
+          <t>146741</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>613624</t>
+          <t>613944</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>640954</t>
+          <t>640473</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>592828</t>
+          <t>592250</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>624676</t>
+          <t>624284</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1215589</t>
+          <t>1215609</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1257090</t>
+          <t>1256246</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,21%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61799</t>
+          <t>62780</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93731</t>
+          <t>93775</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>78061</t>
+          <t>75911</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>114368</t>
+          <t>115563</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>149355</t>
+          <t>147142</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>197823</t>
+          <t>197131</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>848491</t>
+          <t>848447</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>880423</t>
+          <t>879442</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>924244</t>
+          <t>923049</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>960551</t>
+          <t>962701</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1783011</t>
+          <t>1783703</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1831479</t>
+          <t>1833692</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,57%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>229997</t>
+          <t>227814</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>291763</t>
+          <t>290827</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>312640</t>
+          <t>312230</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>385338</t>
+          <t>383320</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>561635</t>
+          <t>562402</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>658087</t>
+          <t>654366</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2984780</t>
+          <t>2985716</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3046546</t>
+          <t>3048729</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2993859</t>
+          <t>2995877</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3066557</t>
+          <t>3066967</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5997654</t>
+          <t>6001375</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6094106</t>
+          <t>6093339</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,55%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>75195</t>
+          <t>74521</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>110301</t>
+          <t>111084</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>86637</t>
+          <t>86511</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>127587</t>
+          <t>127230</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>173186</t>
+          <t>169923</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>226040</t>
+          <t>226582</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>593168</t>
+          <t>592385</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>628274</t>
+          <t>628948</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>569463</t>
+          <t>569820</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>610413</t>
+          <t>610539</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1174479</t>
+          <t>1173937</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1227333</t>
+          <t>1230596</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,87%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>95793</t>
+          <t>95639</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>136128</t>
+          <t>135774</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>122974</t>
+          <t>121410</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>168813</t>
+          <t>168520</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>231983</t>
+          <t>231537</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>292758</t>
+          <t>292483</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>881819</t>
+          <t>882173</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>922154</t>
+          <t>922308</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>860160</t>
+          <t>860453</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>905999</t>
+          <t>907563</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1754163</t>
+          <t>1754438</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1814938</t>
+          <t>1815384</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,69%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59330</t>
+          <t>59050</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>96565</t>
+          <t>97625</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>81082</t>
+          <t>78798</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>120011</t>
+          <t>121053</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>150866</t>
+          <t>148400</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>208958</t>
+          <t>201145</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>659650</t>
+          <t>658590</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>696885</t>
+          <t>697165</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>657163</t>
+          <t>656121</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>696092</t>
+          <t>698376</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1324431</t>
+          <t>1332244</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1382523</t>
+          <t>1384989</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,32%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84995</t>
+          <t>87134</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>127349</t>
+          <t>130391</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>119954</t>
+          <t>119570</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>167834</t>
+          <t>164087</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>215348</t>
+          <t>219783</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>276389</t>
+          <t>280807</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>820390</t>
+          <t>817348</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>862744</t>
+          <t>860605</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>884067</t>
+          <t>887814</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>931947</t>
+          <t>932331</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1723251</t>
+          <t>1718833</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1784292</t>
+          <t>1779857</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,01%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>349516</t>
+          <t>351376</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>429276</t>
+          <t>433553</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>448403</t>
+          <t>446382</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>533428</t>
+          <t>532027</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>822841</t>
+          <t>821373</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>934543</t>
+          <t>935342</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2996094</t>
+          <t>2991817</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3075854</t>
+          <t>3073994</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3021670</t>
+          <t>3023071</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3106695</t>
+          <t>3108716</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6045926</t>
+          <t>6045127</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6157628</t>
+          <t>6159096</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,23%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>69148</t>
+          <t>67463</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>105302</t>
+          <t>101912</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>83832</t>
+          <t>85822</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>122660</t>
+          <t>123807</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>160806</t>
+          <t>161934</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>211512</t>
+          <t>212220</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>569498</t>
+          <t>572888</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>605652</t>
+          <t>607337</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>550179</t>
+          <t>549032</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>589007</t>
+          <t>587017</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1136127</t>
+          <t>1135419</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1186833</t>
+          <t>1185705</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,98%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>101351</t>
+          <t>102777</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>143163</t>
+          <t>144257</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>129565</t>
+          <t>129340</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>177231</t>
+          <t>180086</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>244271</t>
+          <t>245270</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>310549</t>
+          <t>311004</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,06%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>879268</t>
+          <t>878174</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>921080</t>
+          <t>919654</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>865682</t>
+          <t>862827</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>913348</t>
+          <t>913573</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1754795</t>
+          <t>1754340</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1821073</t>
+          <t>1820074</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,12%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76988</t>
+          <t>76834</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>114616</t>
+          <t>112368</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>69071</t>
+          <t>70801</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>106560</t>
+          <t>108804</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>159119</t>
+          <t>158936</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>209647</t>
+          <t>210563</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>644936</t>
+          <t>647184</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>682564</t>
+          <t>682718</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>678451</t>
+          <t>676207</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>715940</t>
+          <t>714210</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1334916</t>
+          <t>1334000</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1385444</t>
+          <t>1385627</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,71%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71013</t>
+          <t>71323</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>106571</t>
+          <t>107834</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>105439</t>
+          <t>105268</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>151817</t>
+          <t>149557</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>185117</t>
+          <t>186823</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>244724</t>
+          <t>246002</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,42%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>830996</t>
+          <t>829733</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>866554</t>
+          <t>866244</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>891962</t>
+          <t>894222</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>938340</t>
+          <t>938511</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1736622</t>
+          <t>1735344</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1796229</t>
+          <t>1794523</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,57%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>353501</t>
+          <t>353223</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>427026</t>
+          <t>424568</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>428803</t>
+          <t>427646</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>514035</t>
+          <t>514429</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>802335</t>
+          <t>796559</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>915480</t>
+          <t>914997</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2967324</t>
+          <t>2969782</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3040849</t>
+          <t>3041127</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3030507</t>
+          <t>3030113</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3115739</t>
+          <t>3116896</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6023412</t>
+          <t>6023895</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6136557</t>
+          <t>6142333</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,52%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>94653</t>
+          <t>102956</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>79557</t>
+          <t>86570</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>113500</t>
+          <t>120247</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>118801</t>
+          <t>126463</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>106029</t>
+          <t>112488</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>133175</t>
+          <t>141946</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>213454</t>
+          <t>229419</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>191591</t>
+          <t>207914</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>235167</t>
+          <t>252678</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,77%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>540239</t>
+          <t>587194</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>521392</t>
+          <t>569903</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>555335</t>
+          <t>603580</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>556036</t>
+          <t>605640</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>541662</t>
+          <t>590157</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>568808</t>
+          <t>619615</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1096275</t>
+          <t>1192834</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1074562</t>
+          <t>1169575</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1118138</t>
+          <t>1214339</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,38%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>634892</t>
+          <t>690150</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>634892</t>
+          <t>690150</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>634892</t>
+          <t>690150</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>674837</t>
+          <t>732103</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>674837</t>
+          <t>732103</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>674837</t>
+          <t>732103</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1309729</t>
+          <t>1422253</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1309729</t>
+          <t>1422253</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1309729</t>
+          <t>1422253</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>132194</t>
+          <t>145288</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58849</t>
+          <t>123995</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>175020</t>
+          <t>167254</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>150594</t>
+          <t>166759</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>132979</t>
+          <t>150198</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>167354</t>
+          <t>186550</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>282787</t>
+          <t>312047</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>188914</t>
+          <t>284411</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>325095</t>
+          <t>339908</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>16,08%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1058541</t>
+          <t>901226</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1015715</t>
+          <t>879260</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1131886</t>
+          <t>922519</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>804688</t>
+          <t>901089</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>787928</t>
+          <t>881298</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>822303</t>
+          <t>917650</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1863230</t>
+          <t>1802315</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1820922</t>
+          <t>1774454</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1957103</t>
+          <t>1829951</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>86,55%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1190735</t>
+          <t>1046514</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1190735</t>
+          <t>1046514</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1190735</t>
+          <t>1046514</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>955282</t>
+          <t>1067848</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>955282</t>
+          <t>1067848</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>955282</t>
+          <t>1067848</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2146017</t>
+          <t>2114362</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2146017</t>
+          <t>2114362</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2146017</t>
+          <t>2114362</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>107777</t>
+          <t>122724</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>90095</t>
+          <t>103510</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>128481</t>
+          <t>143101</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>299899</t>
+          <t>108231</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>115399</t>
+          <t>92059</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>610314</t>
+          <t>124868</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>407676</t>
+          <t>230955</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>222962</t>
+          <t>205315</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>856711</t>
+          <t>257588</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>16,02%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>592277</t>
+          <t>675417</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>571573</t>
+          <t>655040</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>609959</t>
+          <t>694631</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>631940</t>
+          <t>701343</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>321525</t>
+          <t>684706</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>816440</t>
+          <t>717515</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1224217</t>
+          <t>1376760</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>775182</t>
+          <t>1350127</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1408931</t>
+          <t>1402400</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>87,23%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>700054</t>
+          <t>798141</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>700054</t>
+          <t>798141</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>700054</t>
+          <t>798141</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>931839</t>
+          <t>809574</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>931839</t>
+          <t>809574</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>931839</t>
+          <t>809574</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1631893</t>
+          <t>1607715</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1631893</t>
+          <t>1607715</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1631893</t>
+          <t>1607715</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>130027</t>
+          <t>135637</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>111372</t>
+          <t>117635</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>148859</t>
+          <t>156808</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>187025</t>
+          <t>198032</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>152801</t>
+          <t>177519</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>213090</t>
+          <t>219249</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>317052</t>
+          <t>333669</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>280104</t>
+          <t>307861</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>348317</t>
+          <t>366083</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>796071</t>
+          <t>853614</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>777239</t>
+          <t>832443</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>814726</t>
+          <t>871616</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>903872</t>
+          <t>918526</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>877807</t>
+          <t>897309</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>938096</t>
+          <t>939039</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1699943</t>
+          <t>1772141</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1668678</t>
+          <t>1739727</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1736891</t>
+          <t>1797949</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>85,38%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926098</t>
+          <t>989251</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926098</t>
+          <t>989251</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926098</t>
+          <t>989251</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1090897</t>
+          <t>1116558</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1090897</t>
+          <t>1116558</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1090897</t>
+          <t>1116558</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2016995</t>
+          <t>2105810</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2016995</t>
+          <t>2105810</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2016995</t>
+          <t>2105810</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>464651</t>
+          <t>506606</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>365988</t>
+          <t>468873</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>515380</t>
+          <t>550434</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>756318</t>
+          <t>599485</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>572572</t>
+          <t>564001</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1282956</t>
+          <t>633319</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1220969</t>
+          <t>1106090</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1019748</t>
+          <t>1055483</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1924356</t>
+          <t>1159513</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2987129</t>
+          <t>3017451</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2936400</t>
+          <t>2973623</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3085792</t>
+          <t>3055184</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2896537</t>
+          <t>3126598</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2369899</t>
+          <t>3092764</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3080283</t>
+          <t>3162082</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5883666</t>
+          <t>6144050</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5180279</t>
+          <t>6090627</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6084887</t>
+          <t>6194657</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,44%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3451780</t>
+          <t>3524057</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3451780</t>
+          <t>3524057</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3451780</t>
+          <t>3524057</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3652855</t>
+          <t>3726083</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3652855</t>
+          <t>3726083</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3652855</t>
+          <t>3726083</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7104635</t>
+          <t>7250140</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7104635</t>
+          <t>7250140</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7104635</t>
+          <t>7250140</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
